--- a/recipes/onion-garlic-free-indian/focus-states/15-gujarat/excel/gujarat-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/15-gujarat/excel/gujarat-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ringan no olo (roasted brinjal, no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ringan no olo (roasted brinjal, no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Side  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1749,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Mash roasted flesh. Mix. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron grill or steel oven tray — never aluminium foil. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Mash roasted flesh. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Mix. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>No onion. Work in Cast-iron grill or steel oven tray — never aluminium foil. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 77  ·  Protein 0 g  ·  Carbs 3 g  ·  Fat 7 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Ringan no olo (roasted brinjal, no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1790,7 +1972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1984,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Batata nu shaak (dry potato, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Batata nu shaak (dry potato, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1812,7 +1994,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Side  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1832,44 +2014,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -1963,31 +2145,223 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="66" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Temper. Potatoes. Cover-cook. Slightly sweet optional jaggery pinch.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Potatoes. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Cover-cook. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Slightly sweet optional jaggery pinch. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 15  ·  Protein 0 g  ·  Carbs 3 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Batata nu shaak (dry potato, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2001,7 +2375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2013,7 +2387,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sambharo (cabbage carrot stir, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sambharo (cabbage carrot stir, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2023,7 +2397,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Side  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2043,44 +2417,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Prep 10 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -2174,31 +2548,197 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="66" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Quick stir. Serve with fafda.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Quick stir. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Serve with fafda. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>kcal 19  ·  Protein 1 g  ·  Carbs 4 g  ·  Fat 0 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="n"/>
+      <c r="C26" s="50" t="n"/>
+      <c r="D26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="72" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>For Sambharo (cabbage carrot stir, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+    </row>
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="25">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2212,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2224,7 +2764,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Thepla (methi, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Thepla (methi, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2234,7 +2774,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Bread  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2254,44 +2794,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2421,33 +2961,225 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Knead. Roll thin. Cook on tawa. Travel staple.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Knead. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Roll thin. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook on tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Travel staple. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 369  ·  Protein 13 g  ·  Carbs 73 g  ·  Fat 4 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Thepla (methi, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2461,7 +3193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2473,7 +3205,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Rotli (Gujarati phulka)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Rotli (Gujarati phulka)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2483,7 +3215,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Bread  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2503,44 +3235,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2634,31 +3366,210 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Roll thin. Tawa then puff. Ghee.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Roll thin. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Tawa then puff. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Ghee. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 612  ·  Protein 22 g  ·  Carbs 130 g  ·  Fat 3 g  ·  Fibre 20 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Rotli (Gujarati phulka): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="26">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2672,7 +3583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2684,7 +3595,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Bajri no rotlo (pearl millet)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Bajri no rotlo (pearl millet)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2694,7 +3605,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Bread  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2714,44 +3625,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2845,31 +3756,210 @@
       <c r="C16" s="46" t="n"/>
       <c r="D16" s="46" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B17" s="48" t="inlineStr">
         <is>
-          <t>Pat thick rotlo. Cook on tawa. Serve with ringan no olo.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C17" s="49" t="n"/>
       <c r="D17" s="49" t="n"/>
     </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="54" customHeight="1">
+      <c r="A19" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="48" t="inlineStr">
+        <is>
+          <t>Pat thick rotlo. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cook on tawa. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Serve with ringan no olo. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 650  ·  Protein 22 g  ·  Carbs 121 g  ·  Fat 9 g  ·  Fibre 20 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Bajri no rotlo (pearl millet): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="26">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="B18:D18"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2883,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2895,7 +3985,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Mohanthal (besan fudge)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Mohanthal (besan fudge)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2905,7 +3995,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Sweet  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2925,44 +4015,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 20 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -3092,33 +4182,225 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Roast besan in ghee till grainy. Add syrup. Set in greased steel tray. Cut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Roast besan in ghee till grainy. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Add syrup. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Set in greased steel tray. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 918  ·  Protein 13 g  ·  Carbs 125 g  ·  Fat 41 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Mohanthal (besan fudge): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3132,7 +4414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3144,7 +4426,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Basundi (reduced milk)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Basundi (reduced milk)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3154,7 +4436,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Sweet  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3174,44 +4456,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>Prep 10 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -3323,32 +4605,211 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Reduce milk. Sugar, nuts. Serve warm or chilled.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Reduce milk. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Sugar, nuts. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Serve warm or chilled. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 393  ·  Protein 16 g  ·  Carbs 44 g  ·  Fat 18 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Basundi (reduced milk): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3362,7 +4823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3374,7 +4835,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sukhdi / golpapdi (wheat jaggery)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sukhdi / golpapdi (wheat jaggery)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3384,7 +4845,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Sweet  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3404,44 +4865,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3571,33 +5032,225 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Roast atta in ghee. Mix jaggery off heat. Press in tray. Cut diamonds.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Roast atta in ghee. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Mix jaggery off heat. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Press in tray. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut diamonds. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 685  ·  Protein 7 g  ·  Carbs 80 g  ·  Fat 38 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Sukhdi / golpapdi (wheat jaggery): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3611,7 +5264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3623,7 +5276,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Shrikhand (hung yogurt saffron)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Shrikhand (hung yogurt saffron)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3633,7 +5286,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Dessert  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3653,44 +5306,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Prep 20 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -3802,32 +5455,211 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Whisk. Chill. Serve with puri.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Whisk. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Serve with puri. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 261  ·  Protein 9 g  ·  Carbs 41 g  ·  Fat 8 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Tree nuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Shrikhand (hung yogurt saffron): keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in a steel or glass bowl. Stir at the pass so it is not split or settled. Service temperature: Chilled. Allergen label for this dish: Gluten (wheat); Milk; Tree nuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4105,7 +5937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4117,7 +5949,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Doodhpak (Gujarati rice kheer)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Doodhpak (Gujarati rice kheer)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4127,7 +5959,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Dessert  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4147,44 +5979,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 10 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -4296,32 +6128,198 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Simmer rice in milk till creamy. Sugar, saffron.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Simmer rice in milk till creamy. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Sugar, saffron. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 262  ·  Protein 13 g  ·  Carbs 22 g  ·  Fat 14 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Tree nuts · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Doodhpak (Gujarati rice kheer): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Tree nuts; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="26">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4335,7 +6333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4347,7 +6345,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Aamras (mango pulp)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Aamras (mango pulp)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4357,7 +6355,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Dessert  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4377,44 +6375,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 15 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4526,32 +6524,211 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Pulp. Chill. Serve with puri.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Pulp. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Chill. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Serve with puri. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Chilled.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 12  ·  Protein 0 g  ·  Carbs 3 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Aamras (mango pulp): keep it cold and set before service. Never store yogurt or milk sweets in aluminium. Garnish nuts only if the allergen card allows. Read spice and hing labels if used.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Chilled. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4565,7 +6742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4577,7 +6754,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Kachumber no onion (Gujarati)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Kachumber no onion (Gujarati)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4587,7 +6764,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Salad  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4607,44 +6784,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>0 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Prep 10 min · Cook 0 min</t>
         </is>
       </c>
     </row>
@@ -4864,38 +7041,217 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="54" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Chop. Toss. No onion.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Chop. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>No onion. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>kcal 60  ·  Protein 2 g  ·  Carbs 14 g  ·  Fat 1 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>For Kachumber no onion (Gujarati): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="26" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B40" s="50" t="n"/>
+      <c r="C40" s="50" t="n"/>
+      <c r="D40" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="33">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4909,7 +7265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4921,7 +7277,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Guvar fali salad (cluster bean, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Guvar fali salad (cluster bean, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4931,7 +7287,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Salad  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4951,44 +7307,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -5172,36 +7528,202 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Steam in steamer. Toss.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Steam in steamer. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Toss. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 181  ·  Protein 4 g  ·  Carbs 18 g  ·  Fat 11 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Guvar fali salad (cluster bean, no onion): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5215,7 +7737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5227,7 +7749,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Corn bhel sattvic (no onion sev mix)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Corn bhel sattvic (no onion sev mix)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5237,7 +7759,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Salad  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5257,44 +7779,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 15 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -5406,32 +7928,198 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Toss. No onion chutney — use green chilli-coriander-lemon.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Toss. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>No onion chutney — use green chilli-coriander-lemon. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 680  ·  Protein 0 g  ·  Carbs 4 g  ·  Fat 75 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Corn bhel sattvic (no onion sev mix): squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="26">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7212,7 +9900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7224,7 +9912,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Khaman dhokla (steamed, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Khaman dhokla (steamed, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7234,7 +9922,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Starter  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7254,44 +9942,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -7439,34 +10127,226 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Batter. Steam 15 min in steamer. Temper and pour over.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel steamer and steel thali — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Batter. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Steam 15 min in steamer. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Temper and pour over. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 300  ·  Protein 15 g  ·  Carbs 38 g  ·  Fat 9 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Sesame · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Khaman dhokla (steamed, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Sesame; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="30">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7480,7 +10360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7492,7 +10372,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Khandvi (rolled gram, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Khandvi (rolled gram, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7502,7 +10382,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Starter  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7522,44 +10402,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -7707,34 +10587,239 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Cook slurry in kadai till thick. Spread thin on steel thali. Roll. Temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cook slurry in kadai till thick. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Spread thin on steel thali. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Roll. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 184  ·  Protein 9 g  ·  Carbs 20 g  ·  Fat 7 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Sesame · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Khandvi (rolled gram, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Sesame; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7748,7 +10833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7760,7 +10845,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Fafda (crisp gram strips)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Fafda (crisp gram strips)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7770,7 +10855,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Starter  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -7790,44 +10875,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 25 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -7957,33 +11042,238 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Knead stiff. Press strips. Fry. Serve with papaya sambharo and fried chillies.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Knead stiff. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Press strips. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Fry. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Serve with papaya sambharo and fried chillies. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>kcal 235  ·  Protein 13 g  ·  Carbs 35 g  ·  Fat 4 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B31" s="50" t="n"/>
+      <c r="C31" s="50" t="n"/>
+      <c r="D31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>For Fafda (crisp gram strips): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="30">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -7997,7 +11287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8009,7 +11299,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Undhiyu (winter mixed veg, no onion garlic)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Undhiyu (winter mixed veg, no onion garlic)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8019,7 +11309,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Main  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8039,44 +11329,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>90 min</t>
+          <t>Prep 40 min · Cook 50 min</t>
         </is>
       </c>
     </row>
@@ -8188,45 +11478,224 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Stuff brinjal with masala. Layer veg + muthiya in heavy kadai. Slow cook covered 40 min.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="54" customHeight="1">
       <c r="A19" s="32" t="n">
         <v>2</v>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>No onion garlic — Gujarati sattvic wedding style.</t>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
         </is>
       </c>
       <c r="C19" s="31" t="n"/>
       <c r="D19" s="31" t="n"/>
     </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Stuff brinjal with masala. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Layer veg + muthiya in heavy kadai. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Slow cook covered 40 min. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>No onion garlic — Gujarati sattvic wedding style. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 216  ·  Protein 6 g  ·  Carbs 47 g  ·  Fat 1 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Undhiyu (winter mixed veg, no onion garlic): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8240,7 +11709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8252,7 +11721,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Gujarati kadhi + khichdi (no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Gujarati kadhi + khichdi (no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8262,7 +11731,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Main  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8282,44 +11751,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>50 min</t>
+          <t>Prep 15 min · Cook 35 min</t>
         </is>
       </c>
     </row>
@@ -8431,32 +11900,237 @@
       <c r="C17" s="46" t="n"/>
       <c r="D17" s="46" t="n"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="66" customHeight="1">
       <c r="A18" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Simmer kadhi sweet-sour. Cook khichdi. Temper both. Serve together.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C18" s="49" t="n"/>
       <c r="D18" s="49" t="n"/>
     </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="31" t="n"/>
+    </row>
+    <row r="20" ht="54" customHeight="1">
+      <c r="A20" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B20" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Simmer kadhi sweet-sour. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Cook khichdi. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Temper both. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Serve together. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 196  ·  Protein 6 g  ·  Carbs 35 g  ·  Fat 4 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Gujarati kadhi + khichdi (no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it. Cook or roast besan until the raw smell is gone.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="B17:D17"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -8470,7 +12144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8482,7 +12156,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sev tameta nu shaak (tomato sev, no onion)</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sev tameta nu shaak (tomato sev, no onion)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8492,7 +12166,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Gujarat kitchen  ·  Main  ·  Gujarati and Kathiawadi, including Jain-style</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Gujarat  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -8512,44 +12186,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -8679,33 +12353,225 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Cook tomato masala. Add sev last minute. Serve with rotli.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cook tomato masala. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Add sev last minute. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Serve with rotli. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 7  ·  Protein 0 g  ·  Carbs 2 g  ·  Fat 0 g  ·  Fibre 0 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Sev tameta nu shaak (tomato sev, no onion): keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="29">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
